--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -131,6 +131,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>深创100ETF</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -141,6 +145,10 @@
   <si>
     <t>CCI</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>买卖金额</t>
@@ -165,6 +173,10 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>买卖金额</t>
@@ -2353,7 +2365,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2533,6 +2545,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2542,7 +2557,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2722,6 +2737,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>122000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2764,7 +2782,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2944,6 +2962,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2953,7 +2974,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3133,6 +3154,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>187206.43969950231</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>193867.80757147254</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3175,7 +3199,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3355,6 +3379,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3364,7 +3391,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3544,6 +3571,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>67206.439699502313</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>71867.807571472542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3565,11 +3595,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438256384"/>
-        <c:axId val="438258304"/>
+        <c:axId val="460428800"/>
+        <c:axId val="460430720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438256384"/>
+        <c:axId val="460428800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3612,14 +3642,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438258304"/>
+        <c:crossAx val="460430720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="438258304"/>
+        <c:axId val="460430720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3670,7 +3700,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438256384"/>
+        <c:crossAx val="460428800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3842,7 +3872,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4022,6 +4052,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4031,7 +4064,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4210,6 +4243,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4253,7 +4289,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4433,6 +4469,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4442,7 +4481,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4622,6 +4661,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>43140.497081088128</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>44214.678756661888</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4664,7 +4706,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4844,6 +4886,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4853,7 +4898,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5033,6 +5078,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17140.497081088128</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18214.678756661888</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5054,11 +5102,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438911744"/>
-        <c:axId val="438913664"/>
+        <c:axId val="465577856"/>
+        <c:axId val="465579392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438911744"/>
+        <c:axId val="465577856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5101,14 +5149,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438913664"/>
+        <c:crossAx val="465579392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="438913664"/>
+        <c:axId val="465579392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5159,7 +5207,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438911744"/>
+        <c:crossAx val="465577856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5331,7 +5379,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5511,6 +5559,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5520,7 +5571,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5700,6 +5751,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>129000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>131000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5742,7 +5796,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5922,6 +5976,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5931,7 +5988,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6111,6 +6168,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>201026.69016266201</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>208032.17692068638</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6153,7 +6213,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6333,6 +6393,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6342,7 +6405,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6522,6 +6585,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>72026.690162662009</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>77032.176920686383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6543,11 +6609,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="497046272"/>
-        <c:axId val="497078272"/>
+        <c:axId val="465798656"/>
+        <c:axId val="465800192"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="497046272"/>
+        <c:axId val="465798656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6590,14 +6656,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="497078272"/>
+        <c:crossAx val="465800192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="497078272"/>
+        <c:axId val="465800192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6648,7 +6714,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="497046272"/>
+        <c:crossAx val="465798656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6820,7 +6886,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7000,6 +7066,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7009,7 +7078,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7189,6 +7258,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>122000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>124000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7231,7 +7303,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7411,6 +7483,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7420,7 +7495,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7600,6 +7675,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>190997.66079790759</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>197753.4286074655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7642,7 +7720,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7822,6 +7900,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7831,7 +7912,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8011,6 +8092,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>68997.660797907592</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>73753.428607465496</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8032,11 +8116,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="498555904"/>
-        <c:axId val="498557696"/>
+        <c:axId val="467131392"/>
+        <c:axId val="470382464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="498555904"/>
+        <c:axId val="467131392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8079,14 +8163,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498557696"/>
+        <c:crossAx val="470382464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="498557696"/>
+        <c:axId val="470382464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8137,7 +8221,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498555904"/>
+        <c:crossAx val="467131392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8309,7 +8393,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8489,6 +8573,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8498,7 +8585,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8678,6 +8765,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>122000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8720,7 +8810,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8900,6 +8990,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8909,7 +9002,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9089,6 +9182,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>187206.43969950231</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>193867.80757147254</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9131,7 +9227,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9311,6 +9407,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9320,7 +9419,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9500,6 +9599,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>67206.439699502313</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>71867.807571472542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9521,11 +9623,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="624350336"/>
-        <c:axId val="624351872"/>
+        <c:axId val="501796864"/>
+        <c:axId val="501798784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="624350336"/>
+        <c:axId val="501796864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9568,14 +9670,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624351872"/>
+        <c:crossAx val="501798784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="624351872"/>
+        <c:axId val="501798784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9626,7 +9728,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624350336"/>
+        <c:crossAx val="501796864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10180,7 +10282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12243,6 +12345,35 @@
         <v>67206.439699502313</v>
       </c>
     </row>
+    <row r="63" spans="1:9" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="E63" s="18">
+        <v>151934.01574763237</v>
+      </c>
+      <c r="F63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="G63" s="18">
+        <v>122000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="I63" s="18">
+        <v>71867.807571472542</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12254,7 +12385,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12284,13 +12415,13 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -12311,7 +12442,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="12"/>
     </row>
@@ -12322,7 +12453,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -14481,6 +14612,38 @@
       </c>
       <c r="J62" s="6">
         <v>107.7933992308817</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>0</v>
+      </c>
+      <c r="D63" s="18">
+        <v>0</v>
+      </c>
+      <c r="E63" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F63" s="18">
+        <v>44214.678756661888</v>
+      </c>
+      <c r="G63" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>44214.678756661888</v>
+      </c>
+      <c r="I63" s="18">
+        <v>18214.678756661888</v>
+      </c>
+      <c r="J63" s="6">
+        <v>66.335527216233743</v>
       </c>
     </row>
   </sheetData>
@@ -14494,7 +14657,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14525,13 +14688,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -14552,19 +14715,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -14574,7 +14737,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -17439,6 +17602,50 @@
       </c>
       <c r="N62" s="1">
         <v>86.230028778736084</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="E63" s="18">
+        <v>163034.61848677124</v>
+      </c>
+      <c r="F63" s="18">
+        <v>208032.17692068638</v>
+      </c>
+      <c r="G63" s="18">
+        <v>131000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>208032.17692068638</v>
+      </c>
+      <c r="I63" s="18">
+        <v>77032.176920686383</v>
+      </c>
+      <c r="J63" s="6">
+        <v>3.1000018119812012E-2</v>
+      </c>
+      <c r="K63" s="6">
+        <v>4.1362846399915991E-2</v>
+      </c>
+      <c r="L63" s="6">
+        <v>3.1000018119812012E-2</v>
+      </c>
+      <c r="M63" s="6">
+        <v>4.7142971012196826E-2</v>
+      </c>
+      <c r="N63" s="1">
+        <v>87.739159225273681</v>
       </c>
     </row>
   </sheetData>
@@ -17452,7 +17659,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17483,13 +17690,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -17510,28 +17717,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -17541,7 +17748,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -20960,6 +21167,59 @@
       </c>
       <c r="Q62" s="1">
         <v>94.913940221952458</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="E63" s="18">
+        <v>154979.17324472862</v>
+      </c>
+      <c r="F63" s="18">
+        <v>197753.4286074655</v>
+      </c>
+      <c r="G63" s="18">
+        <v>124000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>197753.4286074655</v>
+      </c>
+      <c r="I63" s="18">
+        <v>73753.428607465496</v>
+      </c>
+      <c r="J63" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="K63" s="6">
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="L63" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="M63" s="6">
+        <v>1</v>
+      </c>
+      <c r="N63" s="6">
+        <v>92.929284820646245</v>
+      </c>
+      <c r="O63" s="6">
+        <v>89.001223655693991</v>
+      </c>
+      <c r="P63" s="6">
+        <v>85.066287551131708</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>96.871095864818557</v>
       </c>
     </row>
   </sheetData>
@@ -20973,7 +21233,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23219,6 +23479,38 @@
         <v>67206.439699502313</v>
       </c>
     </row>
+    <row r="63" spans="1:10" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="F63" s="18">
+        <v>151934.01574763237</v>
+      </c>
+      <c r="G63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="H63" s="18">
+        <v>122000</v>
+      </c>
+      <c r="I63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="J63" s="18">
+        <v>71867.807571472542</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="35">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,20 +119,8 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PE</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>深创100ETF</t>
@@ -145,14 +133,6 @@
   <si>
     <t>CCI</t>
     <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MAX</t>
@@ -173,14 +153,6 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -2365,7 +2337,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2548,6 +2520,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2557,7 +2532,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2740,6 +2715,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>122000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>124000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2782,7 +2760,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2965,6 +2943,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2974,7 +2955,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3157,6 +3138,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>193867.80757147254</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>170190.95441836005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3199,7 +3183,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3382,6 +3366,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3391,7 +3378,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3574,6 +3561,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>71867.807571472542</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46190.954418360052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3595,11 +3585,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460428800"/>
-        <c:axId val="460430720"/>
+        <c:axId val="514732800"/>
+        <c:axId val="514734336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="460428800"/>
+        <c:axId val="514732800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3642,14 +3632,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460430720"/>
+        <c:crossAx val="514734336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="460430720"/>
+        <c:axId val="514734336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3700,7 +3690,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460428800"/>
+        <c:crossAx val="514732800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3872,7 +3862,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4055,6 +4045,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4064,7 +4057,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4246,6 +4239,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4289,7 +4285,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4472,6 +4468,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4481,7 +4480,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4664,6 +4663,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>44214.678756661888</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>38358.658472178577</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4706,7 +4708,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4889,6 +4891,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4898,7 +4903,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5081,6 +5086,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>18214.678756661888</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>12358.658472178577</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5102,11 +5110,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="465577856"/>
-        <c:axId val="465579392"/>
+        <c:axId val="514758144"/>
+        <c:axId val="514760064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="465577856"/>
+        <c:axId val="514758144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5149,14 +5157,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465579392"/>
+        <c:crossAx val="514760064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465579392"/>
+        <c:axId val="514760064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5207,7 +5215,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465577856"/>
+        <c:crossAx val="514758144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5379,7 +5387,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5562,6 +5570,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5571,7 +5582,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5754,6 +5765,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>131000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>133000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5796,7 +5810,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5979,6 +5993,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5988,7 +6005,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6171,6 +6188,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>208032.17692068638</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>182479.32157648227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6213,7 +6233,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6396,6 +6416,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6405,7 +6428,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6588,6 +6611,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>77032.176920686383</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>49479.321576482267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6609,11 +6635,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="465798656"/>
-        <c:axId val="465800192"/>
+        <c:axId val="523470336"/>
+        <c:axId val="523471872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="465798656"/>
+        <c:axId val="523470336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6656,14 +6682,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465800192"/>
+        <c:crossAx val="523471872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465800192"/>
+        <c:axId val="523471872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6714,7 +6740,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465798656"/>
+        <c:crossAx val="523470336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6886,7 +6912,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7069,6 +7095,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7078,7 +7107,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7261,6 +7290,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>126000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7303,7 +7335,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7486,6 +7518,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7495,7 +7530,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7678,6 +7713,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>197753.4286074655</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>173561.94374731698</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7720,7 +7758,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7903,6 +7941,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7912,7 +7953,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8095,6 +8136,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>73753.428607465496</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>47561.943747316982</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8116,11 +8160,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467131392"/>
-        <c:axId val="470382464"/>
+        <c:axId val="568746752"/>
+        <c:axId val="568903168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467131392"/>
+        <c:axId val="568746752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8163,14 +8207,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470382464"/>
+        <c:crossAx val="568903168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="470382464"/>
+        <c:axId val="568903168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8221,7 +8265,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467131392"/>
+        <c:crossAx val="568746752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8393,7 +8437,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8576,6 +8620,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8585,7 +8632,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8768,6 +8815,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>122000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>124000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8810,7 +8860,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8993,6 +9043,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9002,7 +9055,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9185,6 +9238,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>193867.80757147254</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>170190.95441836005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9227,7 +9283,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9410,6 +9466,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9419,7 +9478,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9602,6 +9661,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>71867.807571472542</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46190.954418360052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9623,11 +9685,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501796864"/>
-        <c:axId val="501798784"/>
+        <c:axId val="591516800"/>
+        <c:axId val="591518336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501796864"/>
+        <c:axId val="591516800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9670,14 +9732,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501798784"/>
+        <c:crossAx val="591518336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501798784"/>
+        <c:axId val="591518336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9728,7 +9790,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501796864"/>
+        <c:crossAx val="591516800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10282,7 +10344,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12374,6 +12436,35 @@
         <v>71867.807571472542</v>
       </c>
     </row>
+    <row r="64" spans="1:9" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="E64" s="18">
+        <v>153740.70049204151</v>
+      </c>
+      <c r="F64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="G64" s="18">
+        <v>124000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="I64" s="18">
+        <v>46190.954418360052</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12385,7 +12476,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12415,13 +12506,13 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -12442,7 +12533,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K1" s="12"/>
     </row>
@@ -12453,7 +12544,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -14644,6 +14735,38 @@
       </c>
       <c r="J63" s="6">
         <v>66.335527216233743</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>0</v>
+      </c>
+      <c r="D64" s="18">
+        <v>0</v>
+      </c>
+      <c r="E64" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F64" s="18">
+        <v>38358.658472178577</v>
+      </c>
+      <c r="G64" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>38358.658472178577</v>
+      </c>
+      <c r="I64" s="18">
+        <v>12358.658472178577</v>
+      </c>
+      <c r="J64" s="6">
+        <v>-82.62240642203966</v>
       </c>
     </row>
   </sheetData>
@@ -14657,7 +14780,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH63"/>
+  <dimension ref="A1:AH64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14688,13 +14811,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -14715,19 +14838,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -17646,6 +17769,50 @@
       </c>
       <c r="N63" s="1">
         <v>87.739159225273681</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="E64" s="18">
+        <v>164841.30323118038</v>
+      </c>
+      <c r="F64" s="18">
+        <v>182479.32157648227</v>
+      </c>
+      <c r="G64" s="18">
+        <v>133000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>182479.32157648227</v>
+      </c>
+      <c r="I64" s="18">
+        <v>49479.321576482267</v>
+      </c>
+      <c r="J64" s="6">
+        <v>0</v>
+      </c>
+      <c r="K64" s="6">
+        <v>3.446903866659666E-2</v>
+      </c>
+      <c r="L64" s="6">
+        <v>0.16900002956390381</v>
+      </c>
+      <c r="M64" s="6">
+        <v>6.7452480770814657E-2</v>
+      </c>
+      <c r="N64" s="1">
+        <v>51.10121714235116</v>
       </c>
     </row>
   </sheetData>
@@ -17659,7 +17826,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH63"/>
+  <dimension ref="A1:AH64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17690,13 +17857,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -17717,28 +17884,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="19" t="s">
         <v>34</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="O1" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -21220,6 +21387,59 @@
       </c>
       <c r="Q63" s="1">
         <v>96.871095864818557</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="E64" s="18">
+        <v>156785.85798913776</v>
+      </c>
+      <c r="F64" s="18">
+        <v>173561.94374731698</v>
+      </c>
+      <c r="G64" s="18">
+        <v>126000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>173561.94374731698</v>
+      </c>
+      <c r="I64" s="18">
+        <v>47561.943747316982</v>
+      </c>
+      <c r="J64" s="6">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="K64" s="6">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="L64" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="M64" s="6">
+        <v>1</v>
+      </c>
+      <c r="N64" s="6">
+        <v>36.02692764800112</v>
+      </c>
+      <c r="O64" s="6">
+        <v>71.343124986463025</v>
+      </c>
+      <c r="P64" s="6">
+        <v>80.49190002957549</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>53.045574900238108</v>
       </c>
     </row>
   </sheetData>
@@ -21233,7 +21453,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21266,10 +21486,10 @@
         <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>2</v>
@@ -21302,7 +21522,7 @@
         <v>2000</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -23509,6 +23729,38 @@
       </c>
       <c r="J63" s="18">
         <v>71867.807571472542</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="16">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="F64" s="18">
+        <v>153740.70049204151</v>
+      </c>
+      <c r="G64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="H64" s="18">
+        <v>124000</v>
+      </c>
+      <c r="I64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="J64" s="18">
+        <v>46190.954418360052</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -135,6 +135,10 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>MAX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -153,6 +157,14 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖金额</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -2337,7 +2349,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2523,6 +2535,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2532,7 +2547,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2718,6 +2733,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>126000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2760,7 +2778,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2946,6 +2964,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2955,7 +2976,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3141,6 +3162,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>170190.95441836005</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>173267.13463001052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3183,7 +3207,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3369,6 +3393,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3378,7 +3405,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3564,6 +3591,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46190.954418360052</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>47267.134630010522</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3585,11 +3615,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="514732800"/>
-        <c:axId val="514734336"/>
+        <c:axId val="396890880"/>
+        <c:axId val="396892416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="514732800"/>
+        <c:axId val="396890880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3632,14 +3662,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514734336"/>
+        <c:crossAx val="396892416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="514734336"/>
+        <c:axId val="396892416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3690,7 +3720,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514732800"/>
+        <c:crossAx val="396890880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3862,7 +3892,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4048,6 +4078,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4057,7 +4090,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4242,6 +4275,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4285,7 +4321,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4471,6 +4507,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4480,7 +4519,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4666,6 +4705,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>38358.658472178577</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>38601.214425485836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4708,7 +4750,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4894,6 +4936,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4903,7 +4948,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5089,6 +5134,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>12358.658472178577</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12601.214425485836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5110,11 +5158,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="514758144"/>
-        <c:axId val="514760064"/>
+        <c:axId val="396947840"/>
+        <c:axId val="396949760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="514758144"/>
+        <c:axId val="396947840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5157,14 +5205,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514760064"/>
+        <c:crossAx val="396949760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="514760064"/>
+        <c:axId val="396949760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5215,7 +5263,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514758144"/>
+        <c:crossAx val="396947840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5387,7 +5435,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5573,6 +5621,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5582,7 +5633,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5768,6 +5819,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>133000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>135000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5810,7 +5864,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5996,6 +6050,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6005,7 +6062,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6191,6 +6248,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>182479.32157648227</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>185633.20566854317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6233,7 +6293,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6419,6 +6479,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6428,7 +6491,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6614,6 +6677,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>49479.321576482267</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>50633.205668543174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6635,11 +6701,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523470336"/>
-        <c:axId val="523471872"/>
+        <c:axId val="428315776"/>
+        <c:axId val="428484480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523470336"/>
+        <c:axId val="428315776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6682,14 +6748,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523471872"/>
+        <c:crossAx val="428484480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523471872"/>
+        <c:axId val="428484480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6740,7 +6806,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523470336"/>
+        <c:crossAx val="428315776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6912,7 +6978,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7098,6 +7164,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7107,7 +7176,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7293,6 +7362,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>126000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>128000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7335,7 +7407,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7521,6 +7593,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7530,7 +7605,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7716,6 +7791,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>173561.94374731698</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>176659.43996851629</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7758,7 +7836,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7944,6 +8022,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7953,7 +8034,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8139,6 +8220,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>47561.943747316982</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>48659.439968516293</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8160,11 +8244,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="568746752"/>
-        <c:axId val="568903168"/>
+        <c:axId val="448810368"/>
+        <c:axId val="454661248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="568746752"/>
+        <c:axId val="448810368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8207,14 +8291,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568903168"/>
+        <c:crossAx val="454661248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="568903168"/>
+        <c:axId val="454661248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8265,7 +8349,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568746752"/>
+        <c:crossAx val="448810368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8437,7 +8521,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8623,6 +8707,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8632,7 +8719,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8818,6 +8905,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>126000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8860,7 +8950,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9046,6 +9136,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9055,7 +9148,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9241,6 +9334,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>170190.95441836005</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>173267.13463001052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9283,7 +9379,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9469,6 +9565,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9478,7 +9577,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9664,6 +9763,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46190.954418360052</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>47267.134630010522</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9685,11 +9787,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="591516800"/>
-        <c:axId val="591518336"/>
+        <c:axId val="457982720"/>
+        <c:axId val="457985408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="591516800"/>
+        <c:axId val="457982720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9732,14 +9834,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591518336"/>
+        <c:crossAx val="457985408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="591518336"/>
+        <c:axId val="457985408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9790,7 +9892,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591516800"/>
+        <c:crossAx val="457982720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10344,7 +10446,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12465,6 +12567,35 @@
         <v>46190.954418360052</v>
       </c>
     </row>
+    <row r="65" spans="1:9" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="E65" s="18">
+        <v>155536.0326884278</v>
+      </c>
+      <c r="F65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="G65" s="18">
+        <v>126000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="I65" s="18">
+        <v>47267.134630010522</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12476,7 +12607,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12506,7 +12637,7 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>19</v>
@@ -14767,6 +14898,38 @@
       </c>
       <c r="J64" s="6">
         <v>-82.62240642203966</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>0</v>
+      </c>
+      <c r="D65" s="18">
+        <v>0</v>
+      </c>
+      <c r="E65" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F65" s="18">
+        <v>38601.214425485836</v>
+      </c>
+      <c r="G65" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>38601.214425485836</v>
+      </c>
+      <c r="I65" s="18">
+        <v>12601.214425485836</v>
+      </c>
+      <c r="J65" s="6">
+        <v>-90.561561933820059</v>
       </c>
     </row>
   </sheetData>
@@ -14780,7 +14943,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14811,10 +14974,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>2</v>
@@ -14838,19 +15001,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -17813,6 +17976,50 @@
       </c>
       <c r="N64" s="1">
         <v>51.10121714235116</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="E65" s="18">
+        <v>166636.63542756668</v>
+      </c>
+      <c r="F65" s="18">
+        <v>185633.20566854317</v>
+      </c>
+      <c r="G65" s="18">
+        <v>135000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>185633.20566854317</v>
+      </c>
+      <c r="I65" s="18">
+        <v>50633.205668543174</v>
+      </c>
+      <c r="J65" s="6">
+        <v>6.999969482421875E-3</v>
+      </c>
+      <c r="K65" s="6">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="L65" s="6">
+        <v>6.999969482421875E-3</v>
+      </c>
+      <c r="M65" s="6">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="N65" s="1">
+        <v>52.095487833085492</v>
       </c>
     </row>
   </sheetData>
@@ -17826,7 +18033,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17857,13 +18064,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -17884,28 +18091,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -21440,6 +21647,59 @@
       </c>
       <c r="Q64" s="1">
         <v>53.045574900238108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="E65" s="18">
+        <v>158581.19018552406</v>
+      </c>
+      <c r="F65" s="18">
+        <v>176659.43996851629</v>
+      </c>
+      <c r="G65" s="18">
+        <v>128000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>176659.43996851629</v>
+      </c>
+      <c r="I65" s="18">
+        <v>48659.439968516293</v>
+      </c>
+      <c r="J65" s="6">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="K65" s="6">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="L65" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="M65" s="6">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="N65" s="6">
+        <v>31.202982920806502</v>
+      </c>
+      <c r="O65" s="6">
+        <v>57.963077631244182</v>
+      </c>
+      <c r="P65" s="6">
+        <v>72.982292563465052</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>27.924647766802451</v>
       </c>
     </row>
   </sheetData>
@@ -21453,7 +21713,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23763,6 +24023,38 @@
         <v>46190.954418360052</v>
       </c>
     </row>
+    <row r="65" spans="1:10" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="F65" s="18">
+        <v>155536.0326884278</v>
+      </c>
+      <c r="G65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="H65" s="18">
+        <v>126000</v>
+      </c>
+      <c r="I65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="J65" s="18">
+        <v>47267.134630010522</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>
